--- a/ig/document/ValueSet-MedCom-ihe-core-formatcode-VS-TEMP.xlsx
+++ b/ig/document/ValueSet-MedCom-ihe-core-formatcode-VS-TEMP.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-01</t>
+    <t>2026-03-10</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/document/ValueSet-MedCom-ihe-core-formatcode-VS-TEMP.xlsx
+++ b/ig/document/ValueSet-MedCom-ihe-core-formatcode-VS-TEMP.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10</t>
+    <t>2026-04-28</t>
   </si>
   <si>
     <t>Publisher</t>
